--- a/Result/profitability/6838.xlsx
+++ b/Result/profitability/6838.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM21"/>
+  <dimension ref="A1:AM22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3009,6 +3009,133 @@
         <v>115.1</v>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>6838</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>3</v>
+      </c>
+      <c r="D22" t="n">
+        <v>8</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-5</v>
+      </c>
+      <c r="F22" t="n">
+        <v>-153.34</v>
+      </c>
+      <c r="G22" t="n">
+        <v>-76</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>-2501.32%</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>10</v>
+      </c>
+      <c r="J22" t="n">
+        <v>-65</v>
+      </c>
+      <c r="K22" t="n">
+        <v>-68</v>
+      </c>
+      <c r="L22" t="n">
+        <v>-0.45</v>
+      </c>
+      <c r="M22" t="n">
+        <v>-0.20875</v>
+      </c>
+      <c r="N22" t="n">
+        <v>-74.34750000000001</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W22" t="n">
+        <v>-0.35</v>
+      </c>
+      <c r="X22" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>-240.28</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>-2.763745111571199</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>-0.88</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>-2.046511627906977</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>-232.24</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>-2.943472750316857</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK22" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>115.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
